--- a/SHINHWA_QMS_WORKFLOW/99_산출물/3개심사_통합달력_20261027.xlsx
+++ b/SHINHWA_QMS_WORKFLOW/99_산출물/3개심사_통합달력_20261027.xlsx
@@ -109,7 +109,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -150,6 +150,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -515,7 +518,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H28"/>
+  <dimension ref="A1:H29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -538,7 +541,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>※ NQA 통보 확정은 ISO 14001 심사 11/19~20뿐입니다. 나머지는 ChatGPT 자료의 내부 권고일·완료목표이고 SQ 요청 회신 기한만 사용자 지정입니다. IATF 심사 시작일은 미확정(일정통보서 미확보).</t>
+          <t>※ 확정/지정 일정: ISO 14001 심사 11/19~20(NQA 통보), 한온 SQ 심사 12/10(사용자 지정 2026-10-27), SQ 담당자 회신 기한 11/05(사용자 지정). 나머지는 ChatGPT 자료의 내부 권고일·완료목표이며, SQ M1~M9(~11/10)는 심사일 12/10 변경 전 기준이라 재조정 대상입니다. IATF 심사 시작일은 미확정.</t>
         </is>
       </c>
     </row>
@@ -1515,6 +1518,42 @@
         </is>
       </c>
       <c r="H28" s="5" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="n">
+        <v>46366</v>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>목</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>SQ</t>
+        </is>
+      </c>
+      <c r="D29" s="10" t="inlineStr">
+        <is>
+          <t>한온 SQ 심사 일정(사용자 지정 2026-10-27, 변경 전 미정) — 현대 제출 전 사전심사 기준</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>품질경영본부 외 전 부서</t>
+        </is>
+      </c>
+      <c r="F29" s="10" t="inlineStr">
+        <is>
+          <t>사용자 지정</t>
+        </is>
+      </c>
+      <c r="G29" s="5" t="inlineStr">
+        <is>
+          <t>사용자 지시 2026-10-27 / CLAUDE.md</t>
+        </is>
+      </c>
+      <c r="H29" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1527,7 +1566,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F28"/>
+  <dimension ref="A1:F29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2069,6 +2108,26 @@
         <v>1</v>
       </c>
     </row>
+    <row r="29">
+      <c r="A29" s="11" t="n">
+        <v>46366</v>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>목</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>한온 SQ 심사 (사용자 지정)</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="n"/>
+      <c r="E29" s="5" t="n"/>
+      <c r="F29" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2080,7 +2139,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2224,6 +2283,23 @@
         </is>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" s="16" t="inlineStr">
+        <is>
+          <t>SQ 일정 변경</t>
+        </is>
+      </c>
+      <c r="B9" s="16" t="inlineStr">
+        <is>
+          <t>한온 SQ 심사가 12/10로 지정됨. SQ M1~M9(10/26~11/10)와 11/05 모의심사·11/06 최종검토·11/10 준비완료는 변경 전 제안일이라 12/10 기준으로 다시 맞출 수 있음. ISO 14001(11/19~20)과 IATF 서류 일정이 먼저 오므로 SQ 모의심사를 11/23 이후로 미루면 11/05~11/10 겹침이 풀림</t>
+        </is>
+      </c>
+      <c r="C9" s="16" t="inlineStr">
+        <is>
+          <t>SQ 마일스톤을 12/10 기준으로 재조정할지 결정(재조정 시 담당자 회신 기한 11/05는 유지 가능)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
